--- a/text/Al-Mg-Si_COST/P-S.xlsx
+++ b/text/Al-Mg-Si_COST/P-S.xlsx
@@ -1845,13 +1845,22 @@
         <v>0.5641693102999999</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="N29">
+        <v>0.001699859024</v>
+      </c>
+      <c r="O29">
+        <v>-0.0002479645794</v>
+      </c>
+      <c r="P29">
+        <v>-0.001451894444</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -1886,13 +1895,22 @@
         <v>0.6882759985</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="N30">
+        <v>0.00165975416</v>
+      </c>
+      <c r="O30">
+        <v>-0.0002105626927</v>
+      </c>
+      <c r="P30">
+        <v>-0.001449191467</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -1927,13 +1945,22 @@
         <v>0.8168512652</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="N31">
+        <v>0.001620443788</v>
+      </c>
+      <c r="O31">
+        <v>-0.0001826328399</v>
+      </c>
+      <c r="P31">
+        <v>-0.001437810948</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -1968,13 +1995,22 @@
         <v>0.9502043671</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="N32">
+        <v>0.001581999352</v>
+      </c>
+      <c r="O32">
+        <v>-0.0001609488047</v>
+      </c>
+      <c r="P32">
+        <v>-0.001421050548</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2056,13 +2092,22 @@
         <v>1.088648565</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="N34">
+        <v>0.001544521883</v>
+      </c>
+      <c r="O34">
+        <v>-0.0001436110989</v>
+      </c>
+      <c r="P34">
+        <v>-0.001400910784</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -2097,13 +2142,22 @@
         <v>1.232501996</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N35">
+        <v>0.001508112238</v>
+      </c>
+      <c r="O35">
+        <v>-0.0001294270847</v>
+      </c>
+      <c r="P35">
+        <v>-0.001378685153</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -2682,13 +2736,22 @@
         <v>1.168445848</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N47">
+        <v>0.001617986541</v>
+      </c>
+      <c r="O47">
+        <v>-0.0002547938892</v>
+      </c>
+      <c r="P47">
+        <v>-0.001363192652</v>
       </c>
     </row>
     <row r="48" spans="1:16">
